--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -789,8 +789,12 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>175</v>
+      </c>
+      <c r="I8" t="n">
+        <v>35</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
@@ -833,20 +837,20 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -855,171 +859,195 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>175</v>
+      </c>
+      <c r="I10" t="n">
+        <v>35</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司 26.91%的股份</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>张一衡</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>175</v>
+      </c>
+      <c r="I11" t="n">
+        <v>35</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，张一衡直接持有公司 26.77%的股份</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>175</v>
+      </c>
+      <c r="I12" t="n">
+        <v>35</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国敏直接持有公司 26.77%的股份</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>孙仁豪</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>175</v>
+      </c>
+      <c r="I13" t="n">
+        <v>35</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙仁豪直接持有公司 1.92%的股份</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>三联合伙</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>175</v>
+      </c>
+      <c r="I14" t="n">
+        <v>35</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>本次发行前股权结构（截至招股说明书签署日）</t>
+          <t>股份公司设立时股权结构（2018年11月）</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8498</v>
+        <v>8150</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>175</v>
+      </c>
+      <c r="I15" t="n">
+        <v>35</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，高新同华直接持有公司 13.53%的股份</t>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -471,9 +471,7 @@
       <c r="D2" t="n">
         <v>348</v>
       </c>
-      <c r="E2" t="n">
-        <v>1566</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>4.5</v>
       </c>
@@ -494,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +549,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -560,494 +558,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
+          <t>报告期初（2019年初）公司股权结构（整体变更后）</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>500</v>
-      </c>
+        <v>8150</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>175</v>
-      </c>
+          <t>全体股东（以净资产折股）</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8150</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%</t>
+          <t>2018 年 10 月 27 日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150万元。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
+          <t>2019年12月增资后股权结构</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>500</v>
-      </c>
+        <v>8498</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>162.5</v>
-      </c>
+          <t>三联合伙</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>348</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构如下：孙国敏出资162.5万元，占注册资本32.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>三联有限设立时出资结构如下：张松满出资162.5万元，占注册资本32.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>500</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>175</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>500</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国敏货币出资100万元</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>货币出资置换完成后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>500</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>105</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：张松满货币出资105万元</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>175</v>
-      </c>
-      <c r="I8" t="n">
-        <v>35</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2019年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>348</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>本次增资完成后，公司股本结构如下：三联合伙持股348万股</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>175</v>
-      </c>
-      <c r="I10" t="n">
-        <v>35</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>175</v>
-      </c>
-      <c r="I11" t="n">
-        <v>35</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>175</v>
-      </c>
-      <c r="I12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>175</v>
-      </c>
-      <c r="I13" t="n">
-        <v>35</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>32</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>175</v>
-      </c>
-      <c r="I14" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>股份公司设立时股权结构（2018年11月）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>8150</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>175</v>
-      </c>
-      <c r="I15" t="n">
-        <v>35</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018 年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150 万元。</t>
+          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,69 +549,143 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>报告期初（2019年初）公司股权结构（整体变更后）</t>
+          <t>2019年12月增资后股权结构</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8150</v>
+        <v>8498</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>全体股东（以净资产折股）</t>
+          <t>三联合伙</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8150</v>
+        <v>348</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2018 年 10 月 27 日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175 号《验资报告》，验证截至 2018年 10 月 27 日，公司已收到全体股东以净资产折股的方式缴纳的注册资本 8,150万元。</t>
+          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2019年12月增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8498</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>2004年6月公司设立时</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>500</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>348</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>175</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
+          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。孙国奉以货币和设备出资175.0万元，占注册资本35.0%（招股书第30页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2004年6月公司设立时</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。张一衡以货币和设备出资162.5万元，占注册资本32.5%（招股书第30页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2004年6月公司设立时</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>500</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>孙国梅</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。孙国梅以货币和设备出资162.5万元，占注册资本32.5%（招股书第30页）</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,6 @@
       <c r="D2" t="n">
         <v>348</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>4.5</v>
       </c>
@@ -564,7 +564,6 @@
       <c r="D2" t="n">
         <v>8498</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>三联合伙</t>
@@ -573,8 +572,6 @@
       <c r="G2" t="n">
         <v>348</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
@@ -595,7 +592,6 @@
           <t>2004年6月公司设立时</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>500</v>
       </c>
@@ -604,7 +600,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>175</v>
       </c>
@@ -631,7 +626,6 @@
           <t>2004年6月公司设立时</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>500</v>
       </c>
@@ -640,7 +634,6 @@
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
@@ -667,7 +660,6 @@
           <t>2004年6月公司设立时</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>500</v>
       </c>
@@ -676,7 +668,6 @@
           <t>孙国梅</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>162.5</v>
       </c>
@@ -688,6 +679,322 @@
           <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。孙国梅以货币和设备出资162.5万元，占注册资本32.5%（招股书第30页）</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量1条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量4条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>348</v>
+      </c>
+      <c r="F4" t="n">
+        <v>848</v>
+      </c>
+      <c r="G4" t="n">
+        <v>348</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>三联合伙</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>348</v>
+      </c>
+      <c r="F5" t="n">
+        <v>348</v>
+      </c>
+      <c r="G5" t="n">
+        <v>348</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>175</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>175</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-175</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>孙国梅</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-162.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-162.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,27 +456,279 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2004-06-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2004-06-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2004-06-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2007-11-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2007-11-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2007-11-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>孙仁豪</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>39</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>2019-12-04</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>348</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>4.5</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2019年12月4日，公司股东大会审议通过了《关于公司增资扩股的议案》，发行人选择该时点作为授予日，按照7年确认等待期（以2019年12月4日起算，按照公司上市申报计划2023年12月上市，含上市后锁定期3年），根据中水致远股权评估公允价值7.15元/股与4.50元/股的价差按期分摊计入当期费用。</t>
         </is>
       </c>
     </row>
@@ -492,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,32 +800,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2019年12月增资后股权结构</t>
+          <t>三联有限设立时出资结构（2004年6月）</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8498</v>
+        <v>500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>348</v>
-      </c>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>175</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2019年12月4日，公司召开2019年第二次临时股东大会，审议通过了《关于公司增资扩股的议案》，议案决定拟将公司的注册资本由 8,150 万元增加至8,498万元。新增注册资本由新股东三联合伙以每股 4.50元的价格认购，其中 348 万元计入注册资本，剩余 1,218万元计入资本公积。</t>
+          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
         </is>
       </c>
     </row>
@@ -589,26 +845,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2004年6月公司设立时</t>
-        </is>
+          <t>三联有限设立时出资结构（2004年6月）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>500</v>
       </c>
       <c r="E3" t="n">
         <v>500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>175</v>
-      </c>
-      <c r="I3" t="n">
-        <v>35</v>
-      </c>
+        <v>162.5</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。孙国奉以货币和设备出资175.0万元，占注册资本35.0%（招股书第30页）</t>
+          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
         </is>
       </c>
     </row>
@@ -623,378 +881,448 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2004年6月公司设立时</t>
-        </is>
+          <t>三联有限设立时出资结构（2004年6月）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
       </c>
       <c r="E4" t="n">
         <v>500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>张一衡</t>
-        </is>
-      </c>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
-      <c r="I4" t="n">
-        <v>32.5</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。张一衡以货币和设备出资162.5万元，占注册资本32.5%（招股书第30页）</t>
+          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2004年6月公司设立时</t>
-        </is>
+          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
       </c>
       <c r="E5" t="n">
         <v>500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孙国梅</t>
-        </is>
-      </c>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>32.5</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2004年6月1日，孙国奉、张一衡、孙国梅共同签署股东协议及公司章程，约定三联有限的注册资本500万元。孙国梅以货币和设备出资162.5万元，占注册资本32.5%（招股书第30页）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量1条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量4条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>500</v>
       </c>
-      <c r="E4" t="n">
-        <v>348</v>
-      </c>
-      <c r="F4" t="n">
-        <v>848</v>
-      </c>
-      <c r="G4" t="n">
-        <v>348</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-500</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>105</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>股份公司设立时股权结构（2018年10月）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>股份公司设立时股权结构（2018年10月）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>股份公司设立时股权结构（2018年10月）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>股份公司设立时股权结构（2018年10月）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>孙仁豪</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>股份公司设立时股权结构（2018年10月）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>47</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>孙仁豪</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>348</v>
-      </c>
-      <c r="F5" t="n">
-        <v>348</v>
-      </c>
-      <c r="G5" t="n">
-        <v>348</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>175</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>175</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-175</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>孙国梅</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-162.5</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-162.5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,9 +469,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -491,9 +489,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -514,9 +509,6 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -537,9 +529,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -560,9 +549,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -583,9 +569,6 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -606,9 +589,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -629,9 +609,6 @@
           <t>张一衡</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -652,9 +629,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -675,9 +649,6 @@
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -698,9 +669,6 @@
           <t>高新同华</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -721,8 +689,6 @@
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>4.5</v>
       </c>
@@ -823,11 +789,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>175</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -859,11 +823,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>162.5</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -895,11 +857,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -931,11 +891,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>175</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -967,11 +925,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1003,11 +959,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1031,15 +985,11 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1063,15 +1013,11 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1095,15 +1041,11 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1127,15 +1069,11 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1159,15 +1097,11 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1188,16 +1122,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1218,16 +1147,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1248,16 +1172,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1278,16 +1197,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1308,21 +1222,404 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴12条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量16条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" t="n">
+        <v>380</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>175</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>175</v>
+      </c>
+      <c r="G5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-62.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>105</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-57.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>175</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>175</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-175</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,6 +468,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -489,6 +491,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -509,6 +514,9 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -529,6 +537,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -549,6 +560,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -569,6 +583,9 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -589,6 +606,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -609,6 +629,9 @@
           <t>张一衡</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -629,6 +652,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -649,6 +675,9 @@
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -669,6 +698,9 @@
           <t>高新同华</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -689,6 +721,8 @@
           <t>三联合伙</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>4.5</v>
       </c>
@@ -789,9 +823,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>175</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -823,9 +859,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>162.5</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -857,9 +895,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -891,9 +931,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>175</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -925,9 +967,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>100</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -959,9 +1003,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -985,11 +1031,15 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1013,11 +1063,15 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1041,11 +1095,15 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1069,11 +1127,15 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1097,11 +1159,15 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1122,11 +1188,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1147,11 +1218,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1172,11 +1248,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1197,11 +1278,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1222,404 +1308,21 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴12条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量16条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G4" t="n">
-        <v>380</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-120</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>175</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>175</v>
-      </c>
-      <c r="G5" t="n">
-        <v>175</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-62.5</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>105</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-57.5</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>175</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>175</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-175</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>105</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>105</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,9 +469,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -491,9 +489,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -514,9 +509,6 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -537,9 +529,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -560,9 +549,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -583,9 +569,6 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -606,9 +589,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -629,9 +609,6 @@
           <t>张一衡</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -652,9 +629,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -675,9 +649,6 @@
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -698,9 +669,6 @@
           <t>高新同华</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -721,8 +689,6 @@
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>4.5</v>
       </c>
@@ -823,11 +789,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>175</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -859,11 +823,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>162.5</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -895,11 +857,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -931,11 +891,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>175</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -967,11 +925,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1003,11 +959,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1031,15 +985,11 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1063,15 +1013,11 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1095,15 +1041,11 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1127,15 +1069,11 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1159,15 +1097,11 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1188,16 +1122,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1218,16 +1147,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1248,16 +1172,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1278,16 +1197,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1308,20 +1222,175 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴12条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量16条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>380</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-120</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,6 +468,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -489,6 +491,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -509,6 +514,9 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -529,6 +537,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -549,6 +560,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -569,6 +583,9 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -589,6 +606,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -609,6 +629,9 @@
           <t>张一衡</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -629,6 +652,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -649,6 +675,9 @@
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -669,6 +698,9 @@
           <t>高新同华</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -689,6 +721,8 @@
           <t>三联合伙</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>4.5</v>
       </c>
@@ -789,9 +823,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>175</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -823,9 +859,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>162.5</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -857,9 +895,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -891,9 +931,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>175</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -925,9 +967,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>100</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -959,9 +1003,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -985,11 +1031,15 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1013,11 +1063,15 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1041,11 +1095,15 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1069,11 +1127,15 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1097,11 +1159,15 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1122,11 +1188,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1147,11 +1218,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1172,11 +1248,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1197,11 +1278,16 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1222,175 +1308,20 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴12条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量16条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I4" t="n">
-        <v>380</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-120</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,9 +469,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>175</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -491,9 +492,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>162.5</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -514,9 +515,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>162.5</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -537,9 +538,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>175</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -560,9 +561,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -583,9 +584,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>105</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -606,9 +607,6 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -629,9 +627,6 @@
           <t>张一衡</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -652,9 +647,6 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -675,9 +667,6 @@
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -698,9 +687,6 @@
           <t>高新同华</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -721,8 +707,12 @@
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>348</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1566</v>
+      </c>
       <c r="F13" t="n">
         <v>4.5</v>
       </c>
@@ -823,11 +813,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>175</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -859,11 +847,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>162.5</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -895,11 +881,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -931,11 +915,9 @@
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>175</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -967,11 +949,9 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1003,11 +983,9 @@
           <t>张松满</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1031,15 +1009,11 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1063,15 +1037,11 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1095,15 +1065,11 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1127,15 +1093,11 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1159,15 +1121,11 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1188,16 +1146,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1218,16 +1171,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1248,16 +1196,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1278,16 +1221,11 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1308,19 +1246,124 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴12条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量16条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让3条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -607,6 +607,9 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>423</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -813,8 +816,14 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>2287</v>
+      </c>
       <c r="H2" t="n">
         <v>175</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24.43</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -847,8 +856,14 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>2275</v>
+      </c>
       <c r="H3" t="n">
         <v>162.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26.77</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -915,8 +930,14 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>2287</v>
+      </c>
       <c r="H5" t="n">
         <v>175</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24.43</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -949,8 +970,14 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>2275</v>
+      </c>
       <c r="H6" t="n">
         <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>26.77</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1014,6 +1041,15 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>2287</v>
+      </c>
+      <c r="H8" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24.43</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1042,6 +1078,12 @@
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26.77</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1070,6 +1112,12 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I10" t="n">
+        <v>26.77</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1098,6 +1146,12 @@
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>163</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.92</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1126,6 +1180,12 @@
           <t>高新同华</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13.53</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
@@ -1151,6 +1211,15 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>2287</v>
+      </c>
+      <c r="H13" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.43</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1176,6 +1245,12 @@
           <t>张一衡</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26.77</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1201,6 +1276,12 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26.77</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
@@ -1225,6 +1306,12 @@
         <is>
           <t>孙仁豪</t>
         </is>
+      </c>
+      <c r="G16" t="n">
+        <v>163</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.92</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1268,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,12 +1366,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1293,6 +1380,31 @@
         </is>
       </c>
       <c r="E1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1315,11 +1427,12 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1338,32 +1451,700 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让3条</t>
+          <t>总股本</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4724.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>348</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5072.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-405.5</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+      <c r="E5" t="n">
+        <v>2287</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2287</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2287</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2275</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2275</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>105</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-57.5</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>348</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5015</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8150</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3135</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>孙仁豪</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>163</v>
+      </c>
+      <c r="I9" t="n">
+        <v>163</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2287</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2287</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2287</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2275</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2275</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2275</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>105</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-105</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8150</v>
+      </c>
+      <c r="F15" t="n">
+        <v>348</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8498</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1498</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>孙仁豪</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>163</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>163</v>
+      </c>
+      <c r="H16" t="n">
+        <v>163</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2287</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2287</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2287</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2275</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2275</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>张一衡</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2275</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2275</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t0比例合计51.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3股东</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t1比例合计51.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5股东</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t2比例合计93.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5股东</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t3比例合计79.89%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,9 +468,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>175</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -492,9 +493,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>162.5</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -515,9 +518,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>162.5</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
@@ -538,9 +543,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>175</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -561,9 +568,11 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>100</v>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -584,9 +593,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>105</v>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
@@ -607,9 +618,11 @@
           <t>孙国奉</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>423</v>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -630,6 +643,9 @@
           <t>张一衡</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -650,6 +666,9 @@
           <t>孙国敏</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -670,6 +689,9 @@
           <t>孙仁豪</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -690,6 +712,9 @@
           <t>高新同华</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2018年10月27日，华普天健会计师事务所（特殊普通合伙）对公司的出资情况进行了审验，并出具会验字【2018】6175号《验资报告》，验证截至2018年10月27日，公司已收到全体股东以净资产折股的方式缴纳的注册资本8,150万元。</t>
@@ -896,9 +921,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>162.5</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
@@ -1010,9 +1037,11 @@
           <t>张松满</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>105</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
@@ -1036,6 +1065,7 @@
       <c r="D8" t="n">
         <v>8150</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>孙国奉</t>
@@ -1073,6 +1103,7 @@
       <c r="D9" t="n">
         <v>8150</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>张一衡</t>
@@ -1081,6 +1112,7 @@
       <c r="G9" t="n">
         <v>2275</v>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>26.77</v>
       </c>
@@ -1107,6 +1139,7 @@
       <c r="D10" t="n">
         <v>8150</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>孙国敏</t>
@@ -1115,6 +1148,7 @@
       <c r="G10" t="n">
         <v>2275</v>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>26.77</v>
       </c>
@@ -1141,6 +1175,7 @@
       <c r="D11" t="n">
         <v>8150</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>孙仁豪</t>
@@ -1149,6 +1184,7 @@
       <c r="G11" t="n">
         <v>163</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>1.92</v>
       </c>
@@ -1175,6 +1211,7 @@
       <c r="D12" t="n">
         <v>8150</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1183,6 +1220,7 @@
       <c r="G12" t="n">
         <v>1150</v>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>13.53</v>
       </c>
@@ -1206,6 +1244,8 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>孙国奉</t>
@@ -1240,6 +1280,8 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>张一衡</t>
@@ -1248,6 +1290,7 @@
       <c r="G14" t="n">
         <v>2275</v>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>26.77</v>
       </c>
@@ -1271,6 +1314,8 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>孙国敏</t>
@@ -1279,6 +1324,7 @@
       <c r="G15" t="n">
         <v>2275</v>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>26.77</v>
       </c>
@@ -1302,6 +1348,8 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>孙仁豪</t>
@@ -1310,6 +1358,7 @@
       <c r="G16" t="n">
         <v>163</v>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>1.92</v>
       </c>
@@ -1333,818 +1382,19 @@
           <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>三联合伙</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东/认购方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>差额(万股)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴12条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量16条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4724.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>348</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5072.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4667</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-405.5</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2287</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2287</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2287</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2275</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>105</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-57.5</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4667</v>
-      </c>
-      <c r="F8" t="n">
-        <v>348</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5015</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8150</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3135</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>163</v>
-      </c>
-      <c r="I9" t="n">
-        <v>163</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2287</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2287</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2287</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2275</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2275</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>105</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>105</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-105</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1150</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>8150</v>
-      </c>
-      <c r="F15" t="n">
-        <v>348</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8498</v>
-      </c>
-      <c r="H15" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1498</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>163</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>163</v>
-      </c>
-      <c r="H16" t="n">
-        <v>163</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2287</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2287</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2287</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2275</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2275</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-1150</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3股东</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>t0比例合计51.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3股东</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>t1比例合计51.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5股东</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>t2比例合计93.42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>5股东</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>t3比例合计79.89%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -475,7 +475,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -475,7 +475,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2004年6月10日，安徽平泰会计师事务所出具编号为平泰会验字【2004】第395号《验资报告》，验证截至2004年6月10日，三联有限已收到全体股东缴纳的注册资本合计500万元，其中股东孙国奉以实物（机器设备）出资175万元；股东孙国敏以货币出资52.5万元，以实物（机器设备）出资100万元，以代三联有限支付的土地款形成的债权出资10万元，共计162.5万元；股东张松满以货币出资57.5万元，以实物（机器设备）出资105万元，共计162.5万元。</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。 [LLC阶段, 出资额=认购金额, 认购数量不适用]</t>
+          <t>2007年11月26日，安徽平泰会计师事务所出具编号为平泰会验字【2007】第377号《验资报告》，验证截至2007年11月26日，三联有限已收到全体股东380万元货币出资，置换原设立时股东投入的实物资产。其中孙国奉货币出资175万元，孙国敏货币出资100万元，张松满货币出资105万元。三联有限的注册资本仍为500万元。</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,104 +818,88 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>500</v>
-      </c>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>2287</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>175</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>24.43</v>
+        <v>35.48</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
+          <t>Markdown表格: （2）温州三联及三连零部件股本演变概况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E3" t="n">
-        <v>500</v>
-      </c>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>2275</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>162.5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>26.77</v>
+        <v>32.26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
+          <t>Markdown表格: （2）温州三联及三连零部件股本演变概况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构（2004年6月）</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>500</v>
-      </c>
+          <t>（2）温州三联及三连零部件股本演变概况 | 设立时</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>张松满</t>
@@ -923,115 +907,101 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.26</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>三联有限设立时出资结构如下：孙国奉出资175万元，占注册资本35%；孙国敏出资162.5万元，占注册资本32.5%；张松满出资162.5万元，占注册资本32.5%。</t>
+          <t>Markdown表格: （2）温州三联及三连零部件股本演变概况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>500</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>孙国奉</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>2287</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>24.43</v>
+        <v>36.36</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" t="n">
-        <v>500</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>2275</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>26.77</v>
+        <v>27.27</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>货币资金置换实物出资后三联有限的出资结构（2007年11月）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>500</v>
-      </c>
-      <c r="E7" t="n">
-        <v>500</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>张松满</t>
@@ -1039,279 +1009,267 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>105</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>27.27</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>本次货币出资置换完成后，三联有限的出资结构如下：孙国奉货币出资175万元，占注册资本35%；孙国敏货币出资100万元，占注册资本20%；张松满货币出资105万元，占注册资本21%。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年10月）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8150</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2287</v>
-      </c>
+          <t>张银宽&lt;eq&gt;^{注}&lt;/eq&gt;</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>382.5</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>24.43</v>
+        <v>9.1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年10月）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8150</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>107.8</v>
+      </c>
       <c r="I9" t="n">
-        <v>26.77</v>
+        <v>35</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年10月）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>8150</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>45.31</v>
+      </c>
       <c r="I10" t="n">
-        <v>26.77</v>
+        <v>32.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年10月）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>8150</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>163</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>100.1</v>
+      </c>
       <c r="I11" t="n">
-        <v>1.92</v>
+        <v>32.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>股份公司设立时股权结构（2018年10月）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>8150</v>
-      </c>
+          <t>设立时 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>孙国奉</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>276.15</v>
+      </c>
       <c r="I12" t="n">
-        <v>13.53</v>
+        <v>35</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2018年10月11日，孙国奉、张一衡、孙国敏、孙仁豪、高新同华等5名股东作为发起人签署了《发起人协议》，一致同意由三联有限整体变更设立股份公司，股份公司的注册资本为8,150万元。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2287</v>
-      </c>
+          <t>孙国敏</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>382.5</v>
+        <v>256.425</v>
       </c>
       <c r="I13" t="n">
-        <v>24.43</v>
+        <v>32.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>张一衡</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>201.635</v>
+      </c>
       <c r="I14" t="n">
-        <v>26.77</v>
+        <v>32.5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1321,80 +1279,50 @@
           <t>孙国敏</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>2275</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>532.575</v>
+      </c>
       <c r="I15" t="n">
-        <v>26.77</v>
+        <v>67.5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
+          <t>设立时 | 本次增资后</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>孙仁豪</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>163</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>张松满</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>201.635</v>
+      </c>
       <c r="I16" t="n">
-        <v>1.92</v>
+        <v>32.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>截至招股说明书签署日股权结构（含三联合伙增资后）</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>三联合伙</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，孙国奉直接持有公司26.91%的股份，系公司第一大股东，任公司董事长、总经理；张一衡直接持有公司26.77%的股份，任公司董事；孙国敏直接持有公司26.77%的股份；孙仁豪直接持有公司1.92%的股份，任公司副总经理；孙国奉担任三联合伙的执行事务合伙人，可实际支配三联合伙所持有的公司4.10%股份的表决权。</t>
+          <t>Markdown表格: 设立时 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
